--- a/prompts/试验大纲关注要素.xlsx
+++ b/prompts/试验大纲关注要素.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowWidth="23040" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="115">
   <si>
     <t>序号</t>
   </si>
@@ -43,6 +43,12 @@
     <t>第一阶段关注方式</t>
   </si>
   <si>
+    <t>对应规则编号</t>
+  </si>
+  <si>
+    <t>备注说明（是否形成规则/原因）</t>
+  </si>
+  <si>
     <t>试验程序前面章节通用关注点</t>
   </si>
   <si>
@@ -55,15 +61,30 @@
     <t>确定有无</t>
   </si>
   <si>
+    <t>G-01</t>
+  </si>
+  <si>
+    <t>已形成规则（全文规则，封面信息）。</t>
+  </si>
+  <si>
     <t>编号/版本</t>
   </si>
   <si>
+    <t>G-02</t>
+  </si>
+  <si>
     <t>目的</t>
   </si>
   <si>
     <t>第1章</t>
   </si>
   <si>
+    <t>G-03</t>
+  </si>
+  <si>
+    <t>已形成规则（章节规则→第1章 试验目的）。</t>
+  </si>
+  <si>
     <t>范围</t>
   </si>
   <si>
@@ -73,72 +94,168 @@
     <t>确定有无，并与后续试验项进行对比</t>
   </si>
   <si>
+    <t>G-04</t>
+  </si>
+  <si>
+    <t>已形成规则（章节规则→第2章 范围）。</t>
+  </si>
+  <si>
     <t>依据文件</t>
   </si>
   <si>
     <t>全文/一般位于试验程序前面章节</t>
   </si>
   <si>
+    <t>G-05</t>
+  </si>
+  <si>
+    <t>已形成规则（章节规则→第3章 引用文件）。</t>
+  </si>
+  <si>
     <t>受试设备/产品功能描述</t>
   </si>
   <si>
+    <t>G-06</t>
+  </si>
+  <si>
+    <t>已形成规则（章节规则→第6章 试验设备描述）。作为设备信息权威审查方，各试验章节对应项已改为“引用核查”委托至本规则。</t>
+  </si>
+  <si>
     <t>受试设备/产品构型信息，包括软硬件件号、软件版本等信息</t>
   </si>
   <si>
+    <t>G-07</t>
+  </si>
+  <si>
+    <t>已形成规则（章节规则→第6章 试验设备描述）。各试验章节的设备名称/件号/构型类项已改为引用核查委托至本规则。</t>
+  </si>
+  <si>
     <t>受试设备示意图/外形图</t>
   </si>
   <si>
+    <t>G-08</t>
+  </si>
+  <si>
+    <t>已形成规则（章节规则→第6章 试验设备描述）。各试验章节“设备外形”已改为引用核查委托至本规则。</t>
+  </si>
+  <si>
     <t>受试设备轴向示意图</t>
   </si>
   <si>
     <t>全文/一般位于非电磁类文件中</t>
   </si>
   <si>
+    <t>G-09</t>
+  </si>
+  <si>
+    <t>已形成规则（章节规则→第6章 试验设备描述，非电磁类）。</t>
+  </si>
+  <si>
     <t>受试设备交联关系图/文字描述</t>
   </si>
   <si>
+    <t>G-10</t>
+  </si>
+  <si>
+    <t>已形成规则（章节规则→第6章 试验设备描述）。各试验章节“系统架构或交联关系介绍”已改为引用核查委托至本规则。</t>
+  </si>
+  <si>
     <t>受试设备连接器及电缆构型信息</t>
   </si>
   <si>
     <t>全文/一般位于电磁类文件中</t>
   </si>
   <si>
+    <t>G-11</t>
+  </si>
+  <si>
+    <t>已形成规则（章节规则→第6章 试验设备描述，电磁类）。各试验章节“设备/系统线束”已改为引用核查委托至本规则。</t>
+  </si>
+  <si>
     <t>受试设备工作状态/工作模式描述</t>
   </si>
   <si>
+    <t>G-12</t>
+  </si>
+  <si>
+    <t>已形成规则（章节规则→第6章 试验设备描述）。各试验章节“工作模式/被测设备状态”已改为引用核查委托至本规则。</t>
+  </si>
+  <si>
     <t>陪试设备/辅助设备介绍</t>
   </si>
   <si>
+    <t>G-13</t>
+  </si>
+  <si>
+    <t>已形成规则（章节规则→第6章 试验设备描述）。各试验章节“辅助设备/试验辅助设施”已改为引用核查委托至本规则。</t>
+  </si>
+  <si>
     <t>试验项目概述/描述，主要介绍试验项目的试验类别</t>
   </si>
   <si>
     <t>确定有无，并与前后试验项进行对比</t>
   </si>
   <si>
+    <t>G-14</t>
+  </si>
+  <si>
+    <t>已形成规则（章节规则→第7章 试验概述）。注：与各试验章节“鉴定试验类别”非纯重复——本规则为清单层总览，各章为逐科目类别核对，故各章保留未做引用核查。</t>
+  </si>
+  <si>
     <t>试验顺序描述，一般按DO160G要求</t>
   </si>
   <si>
     <t>一般描述为：盐雾试验应在霉菌试验后进行，砂尘试验应在霉菌、盐雾和湿热试验后进行，爆炸大气试验不应在任何其他试验之前进行，可燃性试验不应在任何其他试验之前进行，其余试验顺序不作要求</t>
   </si>
   <si>
+    <t>G-15</t>
+  </si>
+  <si>
+    <t>已形成规则（章节规则→第7章 试验概述-试验项目试验顺序）。</t>
+  </si>
+  <si>
     <t>通用条件描述：包括环境条件、允差、夹具要求等</t>
   </si>
   <si>
+    <t>G-16</t>
+  </si>
+  <si>
+    <t>已形成规则（章节规则→第8章 试验通用要求）。</t>
+  </si>
+  <si>
     <t>试验地点/试验承试单位描述</t>
   </si>
   <si>
+    <t>G-17</t>
+  </si>
+  <si>
+    <t>已形成规则（章节规则→第9章 试验承试单位）。作为承试单位权威审查方，第4/5/6章“试验单位”规则已删除，统一由本规则审查；第15/16/17/25章“实验室或场地要求”、第18/20/22章“试验室资质”为电磁类特定场地要求，保持独立不变。</t>
+  </si>
+  <si>
     <t>试验人员资质要求</t>
   </si>
   <si>
     <t>确定有对试验操作人员的资质要求即可</t>
   </si>
   <si>
+    <t>G-18</t>
+  </si>
+  <si>
+    <t>已形成规则（章节规则→第10章 试验人员）。</t>
+  </si>
+  <si>
     <t>试验前ATP检查</t>
   </si>
   <si>
     <t>需确定试验前已完成ATP此类描述即可</t>
   </si>
   <si>
+    <t>G-19</t>
+  </si>
+  <si>
+    <t>已形成规则（章节规则→第12章 设备功能检查/ATP）。</t>
+  </si>
+  <si>
     <t>试验异常情况处理/方案</t>
   </si>
   <si>
@@ -148,12 +265,30 @@
     <t>确认有无</t>
   </si>
   <si>
+    <t>G-20</t>
+  </si>
+  <si>
+    <t>已形成规则（全文规则，异常处理无独立章节，散见全文）。</t>
+  </si>
+  <si>
     <t>试验中止和恢复的处理/方案</t>
   </si>
   <si>
+    <t>G-21</t>
+  </si>
+  <si>
+    <t>已形成规则（章节规则→第35章 试验的终止与恢复处理）。</t>
+  </si>
+  <si>
     <t>规定试验报告内容</t>
   </si>
   <si>
+    <t>G-22</t>
+  </si>
+  <si>
+    <t>已形成规则（章节规则→第36章 试验报告有关要求）。</t>
+  </si>
+  <si>
     <t>试验程序章节通用关注点</t>
   </si>
   <si>
@@ -163,33 +298,54 @@
     <t>一般位于试验程序第1小节</t>
   </si>
   <si>
+    <t>—（未形成规则）</t>
+  </si>
+  <si>
+    <t>未形成独立规则。原因：与各试验章节规则中已有的“试验目的”检查项重复，逐章审查即可，无需再设通用规则。</t>
+  </si>
+  <si>
     <t>试验条件</t>
   </si>
   <si>
     <t>一般位于试验程序第2小节</t>
   </si>
   <si>
+    <t>未形成独立规则。原因：与各试验章节“试验要求/试验条件”检查项重复，逐章审查更贴合各科目具体条件。</t>
+  </si>
+  <si>
     <t>受试设备/陪试设备要求</t>
   </si>
   <si>
     <t>可引用前序章节/也可单独描述</t>
   </si>
   <si>
+    <t>未形成独立规则。原因：受试/陪试设备信息由G-06~G-13（第6章）统一审查，各试验章节对应项已改为引用核查，无需再设通用规则。</t>
+  </si>
+  <si>
     <t>测试设备、用途、精度及校准周期/有效期</t>
   </si>
   <si>
     <t>一般位于试验程序第前序小节</t>
   </si>
   <si>
+    <t>未形成独立规则。原因：与各试验章节“试验设备/试验仪器”检查项重复，且测试设备精度/校准因科目而异，逐章审查更合适。</t>
+  </si>
+  <si>
     <t>试验连接图/布置图</t>
   </si>
   <si>
+    <t>未形成独立规则。原因：与各试验章节“试验布置要求/试验布置和连接”检查项重复，布置图逐科目不同，逐章审查更合适。</t>
+  </si>
+  <si>
     <t>电搭接要求</t>
   </si>
   <si>
     <t>一般位于电磁类试验项目中</t>
   </si>
   <si>
+    <t>未形成独立规则。原因：与电磁类各章“设备电搭接和接地”检查项重复，且为电磁类特定要求，保留在各章。</t>
+  </si>
+  <si>
     <t>试验前后功能性能检查</t>
   </si>
   <si>
@@ -199,16 +355,25 @@
     <t>确认有无试验前功能性能/QPAT等此类描述，用于检查试验件</t>
   </si>
   <si>
+    <t>未形成独立规则。原因：与各试验章节功能性能检查及第12章“设备功能检查(ATP/QPAT)”重复，已由G-19覆盖前置ATP。</t>
+  </si>
+  <si>
     <t>试验前准备</t>
   </si>
   <si>
     <t>确认有无关于试验装置布置、安装等描述</t>
   </si>
   <si>
+    <t>未形成独立规则。原因：与各试验章节“受试设备、试验装置(试验前)的制造符合性要求/设备安装”检查项重复，逐章审查即可。</t>
+  </si>
+  <si>
     <t>试验判据</t>
   </si>
   <si>
     <t>一般位于试验程序后</t>
+  </si>
+  <si>
+    <t>未形成独立规则。原因：与各试验章节“试验合格判据/试验判据”检查项重复，判据逐科目不同，必须逐章审查。</t>
   </si>
 </sst>
 </file>
@@ -221,7 +386,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -240,6 +405,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -596,7 +768,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -633,9 +805,57 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color theme="4"/>
       </left>
+      <right style="thin">
+        <color theme="4"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color theme="4"/>
       </right>
@@ -765,164 +985,166 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="13">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1234,478 +1456,676 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <dimension ref="A1:F34"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="5.66666666666667" style="1" customWidth="1"/>
     <col min="2" max="2" width="46.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="31.7777777777778" style="1" customWidth="1"/>
     <col min="4" max="4" width="58.4444444444444" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="1"/>
+    <col min="5" max="5" width="16" style="1" customWidth="1"/>
+    <col min="6" max="6" width="60" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="16" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="4">
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="9">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="9">
+        <v>2</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="9">
+        <v>3</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="9">
+        <v>4</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="9">
         <v>5</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="B7" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" ht="28.8" spans="1:6">
+      <c r="A8" s="9">
         <v>6</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="B8" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" ht="28.8" customHeight="1" spans="1:6">
+      <c r="A9" s="9">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="4">
+      <c r="B9" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" ht="28.8" spans="1:6">
+      <c r="A10" s="9">
+        <v>8</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="9">
+        <v>9</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" ht="28.8" spans="1:6">
+      <c r="A12" s="9">
+        <v>10</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" ht="28.8" spans="1:6">
+      <c r="A13" s="9">
+        <v>11</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" ht="28.8" spans="1:6">
+      <c r="A14" s="9">
+        <v>12</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" ht="28.8" spans="1:6">
+      <c r="A15" s="9">
+        <v>13</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" ht="43.2" spans="1:6">
+      <c r="A16" s="9">
+        <v>14</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" ht="57.6" customHeight="1" spans="1:6">
+      <c r="A17" s="9">
+        <v>15</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="9">
+        <v>16</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" ht="57.6" spans="1:6">
+      <c r="A19" s="9">
+        <v>17</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="9">
+        <v>18</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="9">
+        <v>19</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="9">
+        <v>20</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="9">
+        <v>21</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="9">
+        <v>22</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+    </row>
+    <row r="26" ht="28.8" spans="1:6">
+      <c r="A26" s="9">
+        <v>1</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" ht="28.8" spans="1:6">
+      <c r="A27" s="9">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B27" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="28" ht="43.2" spans="1:6">
+      <c r="A28" s="9">
+        <v>3</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" ht="28.8" spans="1:6">
+      <c r="A29" s="9">
+        <v>4</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="30" ht="28.8" spans="1:6">
+      <c r="A30" s="9">
+        <v>5</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" ht="28.8" spans="1:6">
+      <c r="A31" s="9">
+        <v>6</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="32" ht="28.8" spans="1:6">
+      <c r="A32" s="9">
+        <v>7</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="33" ht="28.8" spans="1:6">
+      <c r="A33" s="9">
         <v>8</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="B33" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="34" ht="28.8" spans="1:6">
+      <c r="A34" s="9">
         <v>9</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="4">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="4">
-        <v>5</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="4">
-        <v>6</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" ht="28.8" spans="1:4">
-      <c r="A9" s="4">
-        <v>7</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="4">
-        <v>8</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="4">
-        <v>9</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="4">
-        <v>10</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="4">
-        <v>11</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="4">
-        <v>12</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="4">
-        <v>13</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="4">
-        <v>14</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" ht="57.6" spans="1:4">
-      <c r="A17" s="4">
-        <v>15</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="4">
-        <v>16</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="4">
-        <v>17</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="4">
-        <v>18</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="4">
-        <v>19</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="4">
-        <v>20</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="4">
-        <v>21</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="4">
-        <v>22</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="6">
-        <v>1</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="6">
-        <v>2</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="6">
-        <v>3</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="6">
-        <v>4</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="6">
-        <v>5</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="6">
-        <v>6</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="6">
-        <v>7</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="6">
-        <v>8</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="6">
-        <v>9</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>38</v>
+      <c r="B34" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
